--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paolorossi/Documents/uni_appunti/appunti_uni/tpa/tpa-dissipation-PaoloRos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{090740CB-06D3-EB4F-B469-0D57F7FC64E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42F9718-493C-4E46-9B5A-1637AB372F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14780" xr2:uid="{0B275BD5-B885-5448-896B-7DC13FC86C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>RUN</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>sd_par (s)</t>
+  </si>
+  <si>
+    <t>SIZE</t>
   </si>
 </sst>
 </file>
@@ -422,29 +425,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4CD228-75F0-4B49-BA28-96ABC92D38EA}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>100</v>
+      </c>
+      <c r="B2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <f xml:space="preserve"> B2*4*4</f>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <f xml:space="preserve"> B3*4*4</f>
+        <v>8192</v>
       </c>
     </row>
   </sheetData>
